--- a/artfynd/A 61497-2021 artfynd.xlsx
+++ b/artfynd/A 61497-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61497-2021 artfynd.xlsx
+++ b/artfynd/A 61497-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96482597</v>
+        <v>96482641</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660234.4961731718</v>
+        <v>660244</v>
       </c>
       <c r="R2" t="n">
-        <v>7188980.353841159</v>
+        <v>7188954</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96482641</v>
+        <v>96482638</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1596</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660244.0081009946</v>
+        <v>660088</v>
       </c>
       <c r="R3" t="n">
-        <v>7188954.37415415</v>
+        <v>7189015</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96482597</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90932</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>660234</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7188980</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Ingalill  Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61497-2021 artfynd.xlsx
+++ b/artfynd/A 61497-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>